--- a/utils/monday_sprint_sprint_2024-38.xlsx
+++ b/utils/monday_sprint_sprint_2024-38.xlsx
@@ -2835,7 +2835,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>51</v>
@@ -2849,7 +2849,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>18</v>
@@ -2863,7 +2863,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>97</v>

--- a/utils/monday_sprint_sprint_2024-38.xlsx
+++ b/utils/monday_sprint_sprint_2024-38.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="167">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -63,51 +63,54 @@
     <t>25781</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>Melhoria</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>Valor de Venda EXW + Custo de Entrega</t>
+  </si>
+  <si>
+    <t>Bom dia Gentileza criar o relatório de consulta de preço de venda EXW e custo embutido de entrega conforme filtros e relatório anexo. Preciso destes relatório para calculo de comissão EXW e base de calculo de saving de entrega. Aguardo assim que possível.</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>Sistemas</t>
+  </si>
+  <si>
+    <t>27/05/2024</t>
+  </si>
+  <si>
+    <t>24/06/2024</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>6715095059</t>
+  </si>
+  <si>
     <t>Setor não informado</t>
   </si>
   <si>
-    <t>Melhoria</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>Valor de Venda EXW + Custo de Entrega</t>
-  </si>
-  <si>
-    <t>Bom dia Gentileza criar o relatório de consulta de preço de venda EXW e custo embutido de entrega conforme filtros e relatório anexo. Preciso destes relatório para calculo de comissão EXW e base de calculo de saving de entrega. Aguardo assim que possível.</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>27/05/2024</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>Maio</t>
-  </si>
-  <si>
-    <t>22418</t>
-  </si>
-  <si>
     <t>Categoria não informada</t>
   </si>
   <si>
@@ -123,7 +126,10 @@
     <t>Equipe não informada</t>
   </si>
   <si>
-    <t>25206</t>
+    <t>22/06/2024</t>
+  </si>
+  <si>
+    <t>6347644574</t>
   </si>
   <si>
     <t>PDI Eletrônico</t>
@@ -138,7 +144,7 @@
     <t>Março</t>
   </si>
   <si>
-    <t>25418</t>
+    <t>6802430841</t>
   </si>
   <si>
     <t>Melhoria no sistema de Liberação de ensaios e Ensaios destrutivos</t>
@@ -153,7 +159,7 @@
     <t>Junho</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>6758607091</t>
   </si>
   <si>
     <t>Criar processo de Geração Automática das Parcelas na tela de Geração de Eventos de Pagamento</t>
@@ -165,13 +171,16 @@
     <t>Semana 1</t>
   </si>
   <si>
-    <t>25402</t>
+    <t>6802454022</t>
   </si>
   <si>
     <t>Integração da Abertura da CPC e geração da OTF - Parte II</t>
   </si>
   <si>
-    <t>26288</t>
+    <t>23/06/2024</t>
+  </si>
+  <si>
+    <t>6794400494</t>
   </si>
   <si>
     <t>Integração pedidos Sankhya - Análise</t>
@@ -180,10 +189,16 @@
     <t>07/06/2024</t>
   </si>
   <si>
+    <t>18/06/2024</t>
+  </si>
+  <si>
+    <t>6802437700</t>
+  </si>
+  <si>
     <t>Criar Processo de Gestão, que irá Permitir aos Analistas do Comercial, Vincular Quantidades produzidas nos EVENTOS por MODELO e LIGA as CPC´s</t>
   </si>
   <si>
-    <t>22994</t>
+    <t>6811183218</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -195,9 +210,18 @@
     <t>11/06/2024</t>
   </si>
   <si>
+    <t>20/06/2024</t>
+  </si>
+  <si>
+    <t>6811184528</t>
+  </si>
+  <si>
     <t>Exportar apontamentos Moldagem - Paradas</t>
   </si>
   <si>
+    <t>6811185775</t>
+  </si>
+  <si>
     <t>Exportar roteiros por modelo - Usinagem</t>
   </si>
   <si>
@@ -219,7 +243,7 @@
     <t>12/06/2024</t>
   </si>
   <si>
-    <t>26456</t>
+    <t>6837025965</t>
   </si>
   <si>
     <t>Melhoria Movimentação retroativa inspeção</t>
@@ -228,7 +252,7 @@
     <t>14/06/2024</t>
   </si>
   <si>
-    <t>26086</t>
+    <t>6706750074</t>
   </si>
   <si>
     <t>Correção</t>
@@ -240,103 +264,112 @@
     <t>24/05/2024</t>
   </si>
   <si>
-    <t>26119</t>
+    <t>17/06/2024</t>
+  </si>
+  <si>
+    <t>6706761542</t>
   </si>
   <si>
     <t>Erro no apontamento II</t>
   </si>
   <si>
-    <t>26172</t>
+    <t>6704117994</t>
   </si>
   <si>
     <t>Apontamento ajustagem</t>
   </si>
   <si>
-    <t>26253</t>
+    <t>6794497400</t>
   </si>
   <si>
     <t>Projeto Posto de Cópias Eletrônico - Upload de  Documentos</t>
   </si>
   <si>
-    <t>26258</t>
+    <t>09/06/2024</t>
+  </si>
+  <si>
+    <t>6794469324</t>
   </si>
   <si>
     <t>Avaliação de Serviços</t>
   </si>
   <si>
-    <t>26239</t>
+    <t>6794513951</t>
   </si>
   <si>
     <t>[COMPRAS | NIMBI] CRIAÇÃO DE CAMPO MEDIÇÃO NA TELA DE LANÇAMENTO DE NF</t>
   </si>
   <si>
-    <t>26256</t>
+    <t>16/06/2024</t>
+  </si>
+  <si>
+    <t>6794476607</t>
   </si>
   <si>
     <t>Relatório - OTFs Bloqueadas *prioridade*</t>
   </si>
   <si>
-    <t>26153</t>
+    <t>6794761607</t>
   </si>
   <si>
     <t>Processos Robmar</t>
   </si>
   <si>
-    <t>26221</t>
+    <t>6794539256</t>
   </si>
   <si>
     <t>Melhoria na planilha do Pré-produtivo</t>
   </si>
   <si>
-    <t>26205</t>
+    <t>6794546673</t>
   </si>
   <si>
     <t>OPERADOR NÃO CONSEGUE INICIAR PARADA</t>
   </si>
   <si>
-    <t>26260</t>
+    <t>6794458422</t>
   </si>
   <si>
     <t>Relatório Gestão de Estoques</t>
   </si>
   <si>
-    <t>25700</t>
+    <t>6795586279</t>
   </si>
   <si>
     <t>ELIMINAÇÃO DO SETOR 576</t>
   </si>
   <si>
-    <t>26126</t>
+    <t>6794780068</t>
   </si>
   <si>
     <t>Edição de campos do frete de saída</t>
   </si>
   <si>
-    <t>21131</t>
+    <t>6795601349</t>
   </si>
   <si>
     <t>Revisão de fluxo de ACVO</t>
   </si>
   <si>
-    <t>26274</t>
+    <t>6795547827</t>
   </si>
   <si>
     <t>Eliminação de disponibilização em estoque</t>
   </si>
   <si>
-    <t>25701</t>
+    <t>6795556891</t>
   </si>
   <si>
     <t>SEQUÊNCIAS SETOR 610</t>
   </si>
   <si>
-    <t>26312</t>
+    <t>6794335822</t>
   </si>
   <si>
     <t>Apontamento Pintura Web</t>
   </si>
   <si>
-    <t>26421</t>
+    <t>6828107864</t>
   </si>
   <si>
     <t>montar conjunto na entrada deposito fabril</t>
@@ -363,25 +396,25 @@
     <t>Alan Jonis da Silva</t>
   </si>
   <si>
-    <t>26152</t>
+    <t>6807083648</t>
   </si>
   <si>
     <t>[COMPRAS] Campos obrigatórios no cadastro de material</t>
   </si>
   <si>
-    <t>26299</t>
+    <t>6794389169</t>
   </si>
   <si>
     <t>Restrição Acesso Relatório Custeio MP - Sistema de Corridas</t>
   </si>
   <si>
-    <t>26347</t>
+    <t>6807377224</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Relatório Consumo OSI</t>
   </si>
   <si>
-    <t>25880</t>
+    <t>6619641254</t>
   </si>
   <si>
     <t>Melhorias Sistema de Faturamento - Relatório Notas Fiscais Despachadas</t>
@@ -396,7 +429,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-38</t>
+    <t>Mar/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -451,6 +484,9 @@
   </si>
   <si>
     <t>A fazer</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
   </si>
   <si>
     <t>Abertos</t>
@@ -1011,34 +1047,34 @@
         <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>26</v>
@@ -1055,34 +1091,34 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>25</v>
@@ -1097,39 +1133,39 @@
         <v>28</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -1141,42 +1177,42 @@
         <v>27</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>25</v>
@@ -1188,45 +1224,45 @@
         <v>27</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>26</v>
@@ -1235,45 +1271,45 @@
         <v>27</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>26</v>
@@ -1282,42 +1318,42 @@
         <v>27</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>25</v>
@@ -1329,45 +1365,45 @@
         <v>27</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>26</v>
@@ -1376,45 +1412,45 @@
         <v>27</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>26</v>
@@ -1423,45 +1459,45 @@
         <v>27</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>26</v>
@@ -1470,45 +1506,45 @@
         <v>27</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>26</v>
@@ -1517,42 +1553,42 @@
         <v>27</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>25</v>
@@ -1564,45 +1600,45 @@
         <v>27</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>26</v>
@@ -1619,37 +1655,37 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>26</v>
@@ -1666,37 +1702,37 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>26</v>
@@ -1713,37 +1749,37 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>26</v>
@@ -1752,45 +1788,45 @@
         <v>27</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>26</v>
@@ -1799,45 +1835,45 @@
         <v>27</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>26</v>
@@ -1846,45 +1882,45 @@
         <v>27</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>26</v>
@@ -1893,45 +1929,45 @@
         <v>27</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>26</v>
@@ -1940,45 +1976,45 @@
         <v>27</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>26</v>
@@ -1987,45 +2023,45 @@
         <v>27</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>26</v>
@@ -2034,45 +2070,45 @@
         <v>27</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>26</v>
@@ -2081,45 +2117,45 @@
         <v>27</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>26</v>
@@ -2128,45 +2164,45 @@
         <v>27</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>26</v>
@@ -2175,45 +2211,45 @@
         <v>27</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>26</v>
@@ -2222,45 +2258,45 @@
         <v>27</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>26</v>
@@ -2269,45 +2305,45 @@
         <v>27</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>26</v>
@@ -2316,45 +2352,45 @@
         <v>27</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>26</v>
@@ -2363,65 +2399,65 @@
         <v>27</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>17</v>
@@ -2430,25 +2466,25 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>26</v>
@@ -2457,45 +2493,45 @@
         <v>27</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>26</v>
@@ -2504,45 +2540,45 @@
         <v>27</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>26</v>
@@ -2551,45 +2587,45 @@
         <v>27</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>26</v>
@@ -2598,45 +2634,45 @@
         <v>27</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>26</v>
@@ -2645,7 +2681,7 @@
         <v>27</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>29</v>
@@ -2664,23 +2700,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2688,16 +2724,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2708,15 +2744,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J5" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2729,7 +2765,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -2737,7 +2773,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2768,12 +2804,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B2">
         <v>36</v>
@@ -2787,43 +2823,43 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -2832,13 +2868,13 @@
         <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2850,27 +2886,27 @@
         <v>35</v>
       </c>
       <c r="P10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Q10">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E11">
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -2882,27 +2918,27 @@
         <v>36</v>
       </c>
       <c r="M11" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
       <c r="Q11">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -2914,13 +2950,13 @@
         <v>33</v>
       </c>
       <c r="J12" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2929,18 +2965,24 @@
         <v>28</v>
       </c>
       <c r="Q12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2948,13 +2990,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -2962,7 +3004,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2970,7 +3012,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2978,7 +3020,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2986,10 +3028,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2997,7 +3039,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3011,7 +3053,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
@@ -3019,72 +3061,72 @@
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3092,10 +3134,10 @@
         <v>52</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>53</v>
@@ -3103,44 +3145,44 @@
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
